--- a/reviews/review-sheet.xlsx
+++ b/reviews/review-sheet.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>URL(AIに渡す静的版)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -647,9 +647,9 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/</t>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -692,7 +692,7 @@
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/principles/comparison</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/principles/comparison/</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/principles/accessibility</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/principles/accessibility/</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/overview</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/overview/</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/color</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/color/</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/typography</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/typography/</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/writing</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/writing/</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/icon</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/icon/</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/layout-spacing</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/layout-spacing/</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/shape</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/shape/</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/elevation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/elevation/</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/dark-mode</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/dark-mode/</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/adaptive</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/adaptive/</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/interaction-states</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/interaction-states/</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/motion</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/motion/</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/sound</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/sound/</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/input-methods</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/input-methods/</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/keyboard-navigation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/keyboard-navigation/</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr"/>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/actions/button</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/actions/button/</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/actions/fab</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/actions/fab/</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/actions/link</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/actions/link/</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/overview</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/overview/</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/checkbox</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/checkbox/</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/radio</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/radio/</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr"/>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/toggle</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/toggle/</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/slider</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/slider/</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/chips</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/chips/</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/select</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/select/</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/select-patterns</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/select-patterns/</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/menu</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/menu/</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr"/>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/date-time-picker</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/date-time-picker/</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/text-field</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/text-field/</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/search-field</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/search-field/</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/calendar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/calendar/</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/validation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/validation/</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/input-validation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/input-validation/</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/tabs</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/tabs/</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/segmented-control</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/segmented-control/</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/tabs-vs-segmented</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/tabs-vs-segmented/</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/nav-bar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/nav-bar/</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr"/>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/app-bar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/app-bar/</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr"/>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/breadcrumb</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/breadcrumb/</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr"/>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/pagination</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/pagination/</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/dialog</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/dialog/</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr"/>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/fullscreen-dialog</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/fullscreen-dialog/</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr"/>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/side-sheet</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/side-sheet/</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr"/>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/bottom-sheet</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/bottom-sheet/</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/drawer</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/drawer/</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/card</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/card/</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/list</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/list/</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr"/>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/table</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/table/</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/carousel</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/carousel/</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/accordion</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/accordion/</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/overview</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/overview/</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/snackbar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/snackbar/</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/toast</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/toast/</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/tooltip</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/tooltip/</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/progress</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/progress/</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr"/>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/alert</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/alert/</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/badge</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/badge/</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr"/>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/empty-state</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/empty-state/</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/widget</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/widget/</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr"/>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/cross-view</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/cross-view/</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr"/>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>URL(AIに渡す静的版)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -3839,9 +3839,9 @@
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr"/>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/</t>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -3884,7 +3884,7 @@
       <c r="E3" s="7" t="inlineStr"/>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/principles/comparison</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/principles/comparison/</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/principles/accessibility</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/principles/accessibility/</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/overview</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/overview/</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/color</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/color/</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/typography</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/typography/</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/writing</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/writing/</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/icon</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/icon/</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/layout-spacing</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/layout-spacing/</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/shape</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/shape/</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/elevation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/elevation/</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/dark-mode</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/dark-mode/</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/adaptive</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/adaptive/</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/interaction-states</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/interaction-states/</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/motion</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/motion/</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/sound</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/sound/</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/input-methods</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/input-methods/</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/keyboard-navigation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/keyboard-navigation/</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr"/>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/actions/button</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/actions/button/</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/actions/fab</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/actions/fab/</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/actions/link</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/actions/link/</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/overview</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/overview/</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/checkbox</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/checkbox/</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/radio</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/radio/</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr"/>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/toggle</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/toggle/</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/slider</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/slider/</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/chips</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/chips/</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/select</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/select/</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/select-patterns</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/select-patterns/</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/menu</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/menu/</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr"/>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/date-time-picker</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/date-time-picker/</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/text-field</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/text-field/</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr"/>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/search-field</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/search-field/</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/calendar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/calendar/</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr"/>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/validation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/validation/</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/input-validation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/input-validation/</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr"/>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/tabs</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/tabs/</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/segmented-control</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/segmented-control/</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr"/>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/tabs-vs-segmented</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/tabs-vs-segmented/</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr"/>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/nav-bar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/nav-bar/</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr"/>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/app-bar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/app-bar/</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr"/>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/breadcrumb</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/breadcrumb/</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr"/>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/pagination</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/pagination/</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr"/>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/dialog</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/dialog/</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr"/>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/fullscreen-dialog</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/fullscreen-dialog/</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr"/>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/side-sheet</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/side-sheet/</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr"/>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/bottom-sheet</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/bottom-sheet/</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr"/>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/drawer</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/drawer/</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr"/>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/card</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/card/</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/list</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/list/</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr"/>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/table</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/table/</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/carousel</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/carousel/</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr"/>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/accordion</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/accordion/</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/overview</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/overview/</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/snackbar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/snackbar/</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr"/>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/toast</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/toast/</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/tooltip</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/tooltip/</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/progress</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/progress/</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr"/>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/alert</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/alert/</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr"/>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/badge</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/badge/</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr"/>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/empty-state</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/empty-state/</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr"/>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/widget</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/widget/</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr"/>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/cross-view</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/cross-view/</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>URL(AIに渡す静的版)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -7031,9 +7031,9 @@
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr"/>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/</t>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -7076,7 +7076,7 @@
       <c r="E3" s="10" t="inlineStr"/>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/principles/comparison</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/principles/comparison/</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/principles/accessibility</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/principles/accessibility/</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/overview</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/overview/</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/color</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/color/</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/typography</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/typography/</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/writing</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/writing/</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/icon</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/icon/</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/layout-spacing</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/layout-spacing/</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/shape</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/shape/</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/elevation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/elevation/</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/dark-mode</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/dark-mode/</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/adaptive</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/adaptive/</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/interaction-states</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/interaction-states/</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/motion</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/motion/</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/sound</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/sound/</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/input-methods</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/input-methods/</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/tokens/keyboard-navigation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/tokens/keyboard-navigation/</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr"/>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/actions/button</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/actions/button/</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/actions/fab</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/actions/fab/</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/actions/link</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/actions/link/</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/overview</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/overview/</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/checkbox</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/checkbox/</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/radio</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/radio/</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr"/>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/toggle</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/toggle/</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/slider</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/slider/</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/chips</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/chips/</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/select</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/select/</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr"/>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/select-patterns</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/select-patterns/</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr"/>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/menu</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/menu/</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/selection/date-time-picker</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/selection/date-time-picker/</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/text-field</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/text-field/</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr"/>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/search-field</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/search-field/</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr"/>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/calendar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/calendar/</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr"/>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/validation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/validation/</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr"/>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/text-inputs/input-validation</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/text-inputs/input-validation/</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr"/>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/tabs</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/tabs/</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/segmented-control</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/segmented-control/</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr"/>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/tabs-vs-segmented</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/tabs-vs-segmented/</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr"/>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/nav-bar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/nav-bar/</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr"/>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/app-bar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/app-bar/</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/breadcrumb</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/breadcrumb/</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr"/>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/navigation/pagination</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/navigation/pagination/</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr"/>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/dialog</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/dialog/</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr"/>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/fullscreen-dialog</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/fullscreen-dialog/</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr"/>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/side-sheet</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/side-sheet/</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr"/>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/bottom-sheet</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/bottom-sheet/</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr"/>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/drawer</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/drawer/</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr"/>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/card</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/card/</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr"/>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/list</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/list/</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr"/>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/table</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/table/</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr"/>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/carousel</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/carousel/</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/containment/accordion</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/containment/accordion/</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr"/>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/overview</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/overview/</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr"/>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/snackbar</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/snackbar/</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr"/>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/toast</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/toast/</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr"/>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/tooltip</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/tooltip/</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/progress</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/progress/</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/alert</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/alert/</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr"/>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/badge</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/badge/</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr"/>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/empty-state</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/empty-state/</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr"/>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/components/communication/widget</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/components/communication/widget/</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr"/>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>https://izumikawaarisa2026.github.io/designsystem-port/#/cross-view</t>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/cross-view/</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr"/>
@@ -10092,7 +10092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10136,333 +10136,345 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr"/>
-      <c r="B5" s="13" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>静的版と通常版</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AIには「URL」列の静的版(…/designsystem-port/pages/…/)を渡す。本文がHTMLに直接入っていて、JavaScriptを実行できないツールでも読める。タブの切り替えや動きのある見本は、各ページ先頭の「通常版」のリンクから確認する(人のレビューはどちらでもよい)。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr"/>
+      <c r="B6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ステップ</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>誰が / 見る版 → 修正後の版 / 使うシートと列</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>① AIレビュー(1回目)</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Claude・ChatGPT・Gemini(同じページを3つ同時に) / v0.1.0を見る / 「１回目レビュー表」のClaude・ChatGPT・Geminiの列</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>② Claude Code修正</t>
+          <t>① AIレビュー(1回目)</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>3つの指摘を一次情報で確かめて総括し、修正 / → v0.2.0 / 総括・見送った指摘と理由・対応内容(AIの指摘分)</t>
+          <t>Claude・ChatGPT・Gemini(同じページを3つ同時に) / v0.1.0を見る / 「１回目レビュー表」のClaude・ChatGPT・Geminiの列</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>③ 本人レビュー(1回目)</t>
+          <t>② Claude Code修正</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>本人 / v0.2.0を見る / 「１回目レビュー表」の本人の指摘</t>
+          <t>3つの指摘を一次情報で確かめて総括し、修正 / → v0.2.0 / 総括・見送った指摘と理由・対応内容(AIの指摘分)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>④ Claude Code修正</t>
+          <t>③ 本人レビュー(1回目)</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>修正 / → v0.3.0 / 対応内容(本人の指摘分)・対応バージョン・状態</t>
+          <t>本人 / v0.2.0を見る / 「１回目レビュー表」の本人の指摘</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>⑤ AIレビュー(2回目)</t>
+          <t>④ Claude Code修正</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Claude・ChatGPT・Gemini / v0.3.0を見る / 「２回目レビュー表」</t>
+          <t>修正 / → v0.3.0 / 対応内容(本人の指摘分)・対応バージョン・状態</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>⑥ Claude Code修正</t>
+          <t>⑤ AIレビュー(2回目)</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>→ v0.4.0</t>
+          <t>Claude・ChatGPT・Gemini / v0.3.0を見る / 「２回目レビュー表」</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>⑦ 本人レビュー(2回目)</t>
+          <t>⑥ Claude Code修正</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>本人 / v0.4.0を見る / 「２回目レビュー表」の本人の指摘</t>
+          <t>→ v0.4.0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>⑧ Claude Code修正</t>
+          <t>⑦ 本人レビュー(2回目)</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>→ v0.5.0</t>
+          <t>本人 / v0.4.0を見る / 「２回目レビュー表」の本人の指摘</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>⑨ AI最終チェック</t>
+          <t>⑧ Claude Code修正</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Claude・ChatGPT・Gemini / v0.5.0を見る / 「最終レビュー」。修正があれば → v0.6.0</t>
+          <t>→ v0.5.0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
+          <t>⑨ AI最終チェック</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Claude・ChatGPT・Gemini / v0.5.0を見る / 「最終レビュー」。修正があれば → v0.6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
           <t>⑩ 本人最終レビュー</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>本人 / 最新版を見る / 「最終レビュー」。指摘がなくなったら → v1.0.0(完全FIX・正式リリース。検索エンジンに載せる設定に戻す)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr"/>
-      <c r="B17" s="13" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>1行の意味</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>1シート=1回分のレビュー、1行=1ページ。左から「AIの指摘 → 総括 → 対応」、続けて「本人の指摘 → 対応」の順に書く。</t>
-        </is>
-      </c>
+      <c r="A18" s="13" t="inlineStr"/>
+      <c r="B18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>サイト全体の行</t>
+          <t>1行の意味</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>全ページに共通する指摘(用語の統一・デザイン・サイドバーなど)を書く。</t>
+          <t>1シート=1回分のレビュー、1行=1ページ。左から「AIの指摘 → 総括 → 対応」、続けて「本人の指摘 → 対応」の順に書く。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>総括(採用する修正)</t>
+          <t>サイト全体の行</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>AIのレビューの後、3つのAIの指摘をClaude Codeが一次情報で確かめて読み比べ、採用する修正をまとめる。</t>
+          <t>全ページに共通する指摘(用語の統一・デザイン・サイドバーなど)を書く。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>見送った指摘と理由</t>
+          <t>総括(採用する修正)</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>採用しなかった指摘と、その理由(公式の記述と食い違う・既に対応済み など)。</t>
+          <t>AIのレビューの後、3つのAIの指摘をClaude Codeが一次情報で確かめて読み比べ、採用する修正をまとめる。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
+          <t>見送った指摘と理由</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>採用しなかった指摘と、その理由(公式の記述と食い違う・既に対応済み など)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
           <t>対応内容 / 対応バージョン</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>修正した内容と、その修正が入った版(例: v0.2.0)。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr"/>
-      <c r="B23" s="13" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr"/>
+      <c r="B24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>意味</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>まだレビューしていない</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>レビュー済み</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>指摘を書き終えた(修正待ち)</t>
+          <t>まだレビューしていない</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>レビュー済み</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Claude Codeが修正している</t>
+          <t>指摘を書き終えた(修正待ち)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>対応済み</t>
+          <t>対応中</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>修正が終わり、公開URLに反映された</t>
+          <t>Claude Codeが修正している</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>指摘なし</t>
+          <t>対応済み</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>レビューした結果、修正なし</t>
+          <t>修正が終わり、公開URLに反映された</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
+          <t>指摘なし</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>レビューした結果、修正なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
           <t>見送り</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>指摘を確認したが、修正しないと決めた</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr"/>
-      <c r="B31" s="13" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr"/>
+      <c r="B32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Claude Codeとのやり取り</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>このスプレッドシートを「リンクを知っている全員が閲覧可」にしてURLを伝える(Claude Codeは読み込める)。Claude Codeは総括・対応内容などの列を埋めたファイルを返すので、その列を貼り戻す(Claude Codeはこのスプレッドシートを直接は編集できない)。</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr"/>
-      <c r="B33" s="13" t="inlineStr"/>
-    </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr"/>
+      <c r="B34" s="13" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>AIへのレビュー依頼文(ひな形)</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>{ページ名}と{URL}を差し替えて、Claude・ChatGPT・Geminiに同じ文を送る。</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr"/>
-      <c r="B35" s="13" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr"/>
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>次のWebページをレビューしてください。
 デザインシステム比較サイト「DesignSystem Port」の1ページで、Apple(HIG)・Google(Material Design)・W3C(WCAG)・Nielsen Norman Groupの指針を比較し、AIの統合見解(AI解釈)を載せています。
 ページ: {ページ名}
-URL: {URL}
+URL: {URL}(レビュー表の「URL」列の静的版。JavaScriptなしで本文が読める版)
 次の観点で、問題がある箇所だけを具体的に挙げてください(問題がなければ「指摘なし」)。
 1. 事実の誤り(数値・基準番号・公式の記述との食い違い)。可能なら公式ページで確認した根拠を添える
 2. 公式リンクの誤り・リンク切れ

--- a/reviews/review-sheet.xlsx
+++ b/reviews/review-sheet.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="003A4FCF"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="6">
@@ -104,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -151,6 +155,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10092,7 +10101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10114,362 +10123,374 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>公開URL</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
+          <t>公開URL(静的版・AIに渡す)</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>https://izumikawaarisa2026.github.io/designsystem-port/pages/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>公開URL(通常版)</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>https://izumikawaarisa2026.github.io/designsystem-port/</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>リポジトリ</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>https://github.com/izumikawaarisa2026/designsystem-port</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>静的版と通常版</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>AIには「URL」列の静的版(…/designsystem-port/pages/…/)を渡す。本文がHTMLに直接入っていて、JavaScriptを実行できないツールでも読める。タブの切り替えや動きのある見本は、各ページ先頭の「通常版」のリンクから確認する(人のレビューはどちらでもよい)。</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr"/>
-      <c r="B6" s="13" t="inlineStr"/>
-    </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr"/>
+      <c r="B7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>ステップ</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>誰が / 見る版 → 修正後の版 / 使うシートと列</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>① AIレビュー(1回目)</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Claude・ChatGPT・Gemini(同じページを3つ同時に) / v0.1.0を見る / 「１回目レビュー表」のClaude・ChatGPT・Geminiの列</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>② Claude Code修正</t>
+          <t>① AIレビュー(1回目)</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>3つの指摘を一次情報で確かめて総括し、修正 / → v0.2.0 / 総括・見送った指摘と理由・対応内容(AIの指摘分)</t>
+          <t>Claude・ChatGPT・Gemini(同じページを3つ同時に) / v0.1.x(公開中の最新。現在v0.1.2)を見る / 「１回目レビュー表」のClaude・ChatGPT・Geminiの列</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>③ 本人レビュー(1回目)</t>
+          <t>② Claude Code修正</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>本人 / v0.2.0を見る / 「１回目レビュー表」の本人の指摘</t>
+          <t>3つの指摘を一次情報で確かめて総括し、修正 / → v0.2.0 / 総括・見送った指摘と理由・対応内容(AIの指摘分)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>④ Claude Code修正</t>
+          <t>③ 本人レビュー(1回目)</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>修正 / → v0.3.0 / 対応内容(本人の指摘分)・対応バージョン・状態</t>
+          <t>本人 / v0.2.0を見る / 「１回目レビュー表」の本人の指摘</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>⑤ AIレビュー(2回目)</t>
+          <t>④ Claude Code修正</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Claude・ChatGPT・Gemini / v0.3.0を見る / 「２回目レビュー表」</t>
+          <t>修正 / → v0.3.0 / 対応内容(本人の指摘分)・対応バージョン・状態</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>⑥ Claude Code修正</t>
+          <t>⑤ AIレビュー(2回目)</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>→ v0.4.0</t>
+          <t>Claude・ChatGPT・Gemini / v0.3.0を見る / 「２回目レビュー表」</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>⑦ 本人レビュー(2回目)</t>
+          <t>⑥ Claude Code修正</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>本人 / v0.4.0を見る / 「２回目レビュー表」の本人の指摘</t>
+          <t>→ v0.4.0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>⑧ Claude Code修正</t>
+          <t>⑦ 本人レビュー(2回目)</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>→ v0.5.0</t>
+          <t>本人 / v0.4.0を見る / 「２回目レビュー表」の本人の指摘</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>⑨ AI最終チェック</t>
+          <t>⑧ Claude Code修正</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Claude・ChatGPT・Gemini / v0.5.0を見る / 「最終レビュー」。修正があれば → v0.6.0</t>
+          <t>→ v0.5.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
+          <t>⑨ AI最終チェック</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Claude・ChatGPT・Gemini / v0.5.0を見る / 「最終レビュー」。修正があれば → v0.6.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
           <t>⑩ 本人最終レビュー</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>本人 / 最新版を見る / 「最終レビュー」。指摘がなくなったら → v1.0.0(完全FIX・正式リリース。検索エンジンに載せる設定に戻す)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
-      <c r="B18" s="13" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>1行の意味</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>1シート=1回分のレビュー、1行=1ページ。左から「AIの指摘 → 総括 → 対応」、続けて「本人の指摘 → 対応」の順に書く。</t>
-        </is>
-      </c>
+      <c r="A19" s="13" t="inlineStr"/>
+      <c r="B19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>サイト全体の行</t>
+          <t>1行の意味</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>全ページに共通する指摘(用語の統一・デザイン・サイドバーなど)を書く。</t>
+          <t>1シート=1回分のレビュー、1行=1ページ。左から「AIの指摘 → 総括 → 対応」、続けて「本人の指摘 → 対応」の順に書く。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>総括(採用する修正)</t>
+          <t>サイト全体の行</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>AIのレビューの後、3つのAIの指摘をClaude Codeが一次情報で確かめて読み比べ、採用する修正をまとめる。</t>
+          <t>全ページに共通する指摘(用語の統一・デザイン・サイドバーなど)を書く。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>見送った指摘と理由</t>
+          <t>総括(採用する修正)</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>採用しなかった指摘と、その理由(公式の記述と食い違う・既に対応済み など)。</t>
+          <t>AIのレビューの後、3つのAIの指摘をClaude Codeが一次情報で確かめて読み比べ、採用する修正をまとめる。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
+          <t>見送った指摘と理由</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>採用しなかった指摘と、その理由(公式の記述と食い違う・既に対応済み など)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
           <t>対応内容 / 対応バージョン</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>修正した内容と、その修正が入った版(例: v0.2.0)。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr"/>
-      <c r="B24" s="13" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr"/>
+      <c r="B25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>意味</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>まだレビューしていない</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>レビュー済み</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>指摘を書き終えた(修正待ち)</t>
+          <t>まだレビューしていない</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>レビュー済み</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Claude Codeが修正している</t>
+          <t>指摘を書き終えた(修正待ち)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>対応済み</t>
+          <t>対応中</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>修正が終わり、公開URLに反映された</t>
+          <t>Claude Codeが修正している</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>指摘なし</t>
+          <t>対応済み</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>レビューした結果、修正なし</t>
+          <t>修正が終わり、公開URLに反映された</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
+          <t>指摘なし</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>レビューした結果、修正なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
           <t>見送り</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>指摘を確認したが、修正しないと決めた</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr"/>
-      <c r="B32" s="13" t="inlineStr"/>
-    </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr"/>
+      <c r="B33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Claude Codeとのやり取り</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>このスプレッドシートを「リンクを知っている全員が閲覧可」にしてURLを伝える(Claude Codeは読み込める)。Claude Codeは総括・対応内容などの列を埋めたファイルを返すので、その列を貼り戻す(Claude Codeはこのスプレッドシートを直接は編集できない)。</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr"/>
-      <c r="B34" s="13" t="inlineStr"/>
-    </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr"/>
+      <c r="B35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>AIへのレビュー依頼文(ひな形)</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>{ページ名}と{URL}を差し替えて、Claude・ChatGPT・Geminiに同じ文を送る。</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr"/>
-      <c r="B36" s="13" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr"/>
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>次のWebページをレビューしてください。
 デザインシステム比較サイト「DesignSystem Port」の1ページで、Apple(HIG)・Google(Material Design)・W3C(WCAG)・Nielsen Norman Groupの指針を比較し、AIの統合見解(AI解釈)を載せています。
